--- a/辊筒上位机工程/变量表/变量总表.xlsx
+++ b/辊筒上位机工程/变量表/变量总表.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>out_CylUp</t>
+          <t>out_CylValve</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>电磁阀 升线圈(保持至磁开到位)</t>
+          <t>电磁阀线圈(二位五通单电控 得电=升/失电=弹簧降)</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>out_CylDn</t>
+          <t>out_RollerFwd</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>电磁阀 降线圈(保持至磁开到位)</t>
+          <t>C20驱动器 正转端子FWD(断开即停)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Y6</t>
+          <t>Y10</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>out_RollerFwd</t>
+          <t>out_RollerRev</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>C20驱动器 正转端子FWD(断开即停)</t>
+          <t>C20驱动器 反转端子REV(与FWD互斥)</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Y10</t>
+          <t>Y11</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>out_RollerRev</t>
+          <t>out_RollerRst</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1343,59 +1343,15 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>C20驱动器 反转端子REV(与FWD互斥)</t>
+          <t>C20驱动器 复位端子CLR(500ms脉冲)</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Y11</t>
+          <t>Y12</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>out_RollerRst</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>C20驱动器 复位端子CLR(500ms脉冲)</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Y12</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1933,7 +1889,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>bRemoteEn</t>
+          <t>con_EstopActive</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1959,21 +1915,21 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>远程控制允许(=bRunOK且自动位)</t>
+          <t>急停活跃标志(按下或锁存 命令注销门控 防释放后自恢复)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>bModeAuto</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>bRemoteEn</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1981,12 +1937,12 @@
           <t>BOOL</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1999,7 +1955,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>当前模式(TRUE=自动位)</t>
+          <t>远程控制允许(=bRunOK且自动位)</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
@@ -2013,7 +1969,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>con_ResetCmd</t>
+          <t>bModeAuto</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2021,12 +1977,12 @@
           <t>BOOL</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2039,21 +1995,21 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>复位命令(本地+远程边沿合并)</t>
+          <t>当前模式(TRUE=自动位)</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>con_CommLost</t>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>con_ResetCmd</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2079,7 +2035,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>通讯丢失(看门狗Q 心跳恢复自动清除)</t>
+          <t>复位命令(本地+远程边沿合并)</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
@@ -2093,7 +2049,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>bHeartChanged</t>
+          <t>con_CommLost</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2119,7 +2075,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>入向心跳本拍变化标志</t>
+          <t>通讯丢失(看门狗Q 心跳恢复自动清除)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -2133,7 +2089,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>bHeartTiming</t>
+          <t>bHeartChanged</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2159,7 +2115,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>看门狗计时允许(变化拍断IN重启)</t>
+          <t>入向心跳本拍变化标志</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
@@ -2173,20 +2129,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>con_HeartPrev</t>
+          <t>bHeartTiming</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2199,7 +2155,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>入向心跳上次值(初值-1)</t>
+          <t>看门狗计时允许(变化拍断IN重启)</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
@@ -2213,7 +2169,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>con_HeartOut</t>
+          <t>con_HeartPrev</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2224,7 +2180,7 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2239,7 +2195,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>出向心跳计数值(每秒+1)</t>
+          <t>入向心跳上次值(初值-1)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -2253,20 +2209,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>con_HeartTickQ</t>
+          <t>con_HeartOut</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2279,21 +2235,21 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>心跳节拍TONR输出(IN取反自翻转)</t>
+          <t>出向心跳计数值(每秒+1)</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>con_CylTimeout</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>con_HeartTickQ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2319,7 +2275,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>气缸到位超时(悬挂且计时到 接锁存闭环)</t>
+          <t>心跳节拍TONR输出(IN取反自翻转)</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
@@ -2333,7 +2289,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>bCylPending</t>
+          <t>con_CylTimeout</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2359,7 +2315,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>阀命令悬挂未到位(看门狗计时中)</t>
+          <t>气缸到位超时(悬挂且计时到 接锁存闭环)</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
@@ -2373,7 +2329,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>bCylWatchQ</t>
+          <t>bCylPending</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2399,34 +2355,34 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>气缸看门狗TONR输出</t>
+          <t>阀命令悬挂未到位(看门狗计时中)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>con_CylCmd</t>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>bCylWatchQ</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2439,7 +2395,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>阀命令(0=无/1=升/2=降)</t>
+          <t>气缸看门狗TONR输出</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -2453,7 +2409,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>bCylPos</t>
+          <t>con_CylCmd</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2469,7 +2425,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2479,7 +2435,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>阀位记忆(0=未知/1=升位/2=降位 以磁开为准)</t>
+          <t>阀命令(0=无/1=升得电保持/2=降失电弹簧回 单电控)</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
@@ -2493,23 +2449,23 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>bCylUpOn</t>
+          <t>bCylPos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2519,7 +2475,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>升线圈输出中(保持至磁开到位)</t>
+          <t>阀位记忆(0=未知/1=升位/2=降位 以磁开为准)</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
@@ -2533,7 +2489,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>bCylDnOn</t>
+          <t>bCylValveOn</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2559,7 +2515,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>降线圈输出中(保持至磁开到位)</t>
+          <t>阀线圈输出状态(得电=升/失电=降 单电控)</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>

--- a/辊筒上位机工程/变量表/变量总表.xlsx
+++ b/辊筒上位机工程/变量表/变量总表.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="const" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="con" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="host" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能块实例" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hmi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能块实例" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1352,6 +1353,94 @@
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>in_JogRollerFwd</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>手动按钮点动辊筒正转(预留 需扩展输入模块 X10 暂不接线)</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>X10</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>in_JogRollerRev</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>手动按钮点动辊筒反转(预留 需扩展输入模块 X11 暂不接线 与正转互斥)</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>X11</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1694,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2522,14 +2611,14 @@
       <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>bRollerRun</t>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>bJogActive</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2555,7 +2644,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>辊筒正转命令(上位机触发记忆)</t>
+          <t>点动激活标志(任一触摸屏/手动点动输入按下 预留 仅手动位)</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -2569,7 +2658,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>bRollerRev</t>
+          <t>bRollerRun</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2595,7 +2684,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>辊筒反转命令(与正转互斥)</t>
+          <t>辊筒正转命令(上位机触发记忆)</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
@@ -2609,7 +2698,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>bDrvRstPulse</t>
+          <t>bRollerRev</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2635,7 +2724,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>CLR复位端子脉冲中标志</t>
+          <t>辊筒反转命令(与正转互斥)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
@@ -2649,7 +2738,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>bDrvRstHold</t>
+          <t>bDrvRstPulse</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2675,7 +2764,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>CLR复位保持(触发沿置位 到时清除)</t>
+          <t>CLR复位端子脉冲中标志</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
@@ -2689,7 +2778,7 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>bDrvRstEnd</t>
+          <t>bDrvRstHold</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2715,37 +2804,37 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>CLR复位脉冲完成TONR输出</t>
+          <t>CLR复位保持(触发沿置位 到时清除)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>con_SpeedTarget</t>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>bDrvRstEnd</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2755,7 +2844,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>辊筒目标转速(1RPM 0~3000 上位机下发)</t>
+          <t>CLR复位脉冲完成TONR输出</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
@@ -2769,7 +2858,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>con_SpeedLast</t>
+          <t>con_SpeedTarget</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2780,12 +2869,12 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2795,7 +2884,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>已成功写入驱动的转速(变化检测 初值-1)</t>
+          <t>辊筒目标转速(1RPM 0~3000 上位机下发)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
@@ -2809,20 +2898,20 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>bRtuReq</t>
+          <t>con_SpeedLast</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2835,7 +2924,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>RS485待发送请求(转速变化置位)</t>
+          <t>已成功写入驱动的转速(变化检测 初值-1)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
@@ -2849,20 +2938,20 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>dwRtuDataAddr</t>
+          <t>bRtuReq</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DINT</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2875,7 +2964,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>MB_Master目标寄存器地址(指令实参须直接变量)</t>
+          <t>RS485待发送请求(转速变化置位)</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
@@ -2889,16 +2978,20 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>con_RTUBuf</t>
+          <t>dwRtuDataAddr</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>INT[128]</t>
+          <t>DINT</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2911,7 +3004,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>RS485收发缓冲区(写单字取[0])</t>
+          <t>MB_Master目标寄存器地址(指令实参须直接变量)</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
@@ -2925,19 +3018,15 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>bRtuDone</t>
+          <t>con_RTUBuf</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+          <t>INT[128]</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2951,7 +3040,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>MB_Master完成标志</t>
+          <t>RS485收发缓冲区(写单字取[0])</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
@@ -2965,7 +3054,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>bRtuBusy</t>
+          <t>bRtuDone</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2991,7 +3080,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>MB_Master执行中</t>
+          <t>MB_Master完成标志</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
@@ -3005,7 +3094,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>bRtuError</t>
+          <t>bRtuBusy</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3031,7 +3120,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>MB_Master错误标志</t>
+          <t>MB_Master执行中</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
@@ -3045,20 +3134,20 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>dwRtuErrID</t>
+          <t>bRtuError</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DINT</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -3071,11 +3160,51 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>MB_Master错误码</t>
+          <t>MB_Master错误标志</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>dwRtuErrID</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>DINT</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>MB_Master错误码</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4178,6 +4307,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>变量名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>数据类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>隐藏初始值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>初始值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>掉电保持</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>网络公开</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>软元件地址</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>hmi_JogRollerFwd</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>触摸屏点动辊筒正转(按下=TRUE 松开=FALSE 仅手动位)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>hmi_JogRollerRev</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>触摸屏点动辊筒反转(按下=TRUE 松开=FALSE 与正转互斥)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>hmi_JogCylUp</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>触摸屏点动气缸升(按下=TRUE 线圈得电 单电控)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>hmi_JogCylDn</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>触摸屏点动气缸降(按下=TRUE 线圈失电 弹簧复位)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
